--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{995C4895-8476-40C0-9B82-181AFF26B8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40541AAC-3083-47E1-9BF1-5FB1EED0A460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="7590" yWindow="1425" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>dzień wizyty</t>
+  </si>
+  <si>
+    <t>9.08.2026rok</t>
   </si>
 </sst>
 </file>
@@ -109,6 +112,15 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -124,15 +136,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -147,10 +150,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -488,9 +491,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="4:5" ht="243.75" x14ac:dyDescent="0.25">
-      <c r="D7" s="3">
-        <v>46243</v>
+    <row r="7" spans="4:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>1</v>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40541AAC-3083-47E1-9BF1-5FB1EED0A460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF512B6-8DCA-442B-9123-07FA5D2888FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7590" yWindow="1425" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>dzień wizyty</t>
-  </si>
-  <si>
-    <t>9.08.2026rok</t>
   </si>
 </sst>
 </file>
@@ -92,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +102,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,15 +492,17 @@
       </c>
     </row>
     <row r="7" spans="4:5" ht="225" x14ac:dyDescent="0.25">
-      <c r="D7" s="3" t="s">
-        <v>3</v>
+      <c r="D7" s="3">
+        <v>46243</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="1"/>
+      <c r="D8" s="5">
+        <v>45270</v>
+      </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF512B6-8DCA-442B-9123-07FA5D2888FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB24F449-E39E-44B8-85D0-99B69AC55F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>dzień wizyty</t>
+  </si>
+  <si>
+    <t>9.08.2026r.</t>
   </si>
 </sst>
 </file>
@@ -89,21 +92,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -112,12 +109,15 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -150,10 +150,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="0">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -484,114 +484,112 @@
   </cols>
   <sheetData>
     <row r="6" spans="4:5" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="4:5" ht="225" x14ac:dyDescent="0.25">
-      <c r="D7" s="3">
-        <v>46243</v>
+      <c r="D7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="5">
-        <v>45270</v>
-      </c>
-      <c r="E8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB24F449-E39E-44B8-85D0-99B69AC55F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BBF096-FC8F-4692-B4D0-FE1D32B5AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
+  </si>
+  <si>
+    <t>test test</t>
   </si>
 </sst>
 </file>
@@ -150,10 +153,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -500,7 +503,9 @@
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BBF096-FC8F-4692-B4D0-FE1D32B5AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B3990-B595-4E82-9DFF-144460DA8894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <t>9.08.2026r.</t>
   </si>
   <si>
-    <t>test test</t>
+    <t>no i działa</t>
   </si>
 </sst>
 </file>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B3990-B595-4E82-9DFF-144460DA8894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED46834-2483-4469-BCCE-4B28EB469A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
-  </si>
-  <si>
-    <t>no i działa</t>
   </si>
 </sst>
 </file>
@@ -503,9 +500,7 @@
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED46834-2483-4469-BCCE-4B28EB469A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F1E407-224D-4C6A-8CB2-2E13B3C12630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
+  </si>
+  <si>
+    <t>reborn</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,9 @@
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10" s="3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F1E407-224D-4C6A-8CB2-2E13B3C12630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C06226D-EE3E-4B20-B703-1FA0E458B6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
-  </si>
-  <si>
-    <t>reborn</t>
   </si>
 </sst>
 </file>
@@ -508,9 +505,7 @@
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10" s="3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C06226D-EE3E-4B20-B703-1FA0E458B6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC016F9E-D982-4485-966A-F432E9FE8109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="8445" yWindow="1725" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
+  </si>
+  <si>
+    <t>grzegorz stasiecki</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,9 @@
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10" s="3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC016F9E-D982-4485-966A-F432E9FE8109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44FE647-E9E6-407C-9FE1-F497498792A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8445" yWindow="1725" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="5505" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>9.08.2026r.</t>
-  </si>
-  <si>
-    <t>grzegorz stasiecki</t>
   </si>
 </sst>
 </file>
@@ -508,9 +505,7 @@
     </row>
     <row r="9" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D10" s="3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,12 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44FE647-E9E6-407C-9FE1-F497498792A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB37FC5-8EC5-4813-835E-E90721C7D3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5505" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="3255" yWindow="435" windowWidth="33810" windowHeight="15345" tabRatio="653" activeTab="9" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
+    <sheet name="D. Wolniaczyk" sheetId="2" r:id="rId2"/>
+    <sheet name="A. Niedźwiedzki" sheetId="3" r:id="rId3"/>
+    <sheet name="P. Jabłoński" sheetId="4" r:id="rId4"/>
+    <sheet name="E. Grudzińska" sheetId="5" r:id="rId5"/>
+    <sheet name="M. Kusz" sheetId="6" r:id="rId6"/>
+    <sheet name="K. Rybczyński" sheetId="7" r:id="rId7"/>
+    <sheet name="M. Rączka" sheetId="8" r:id="rId8"/>
+    <sheet name="K. Wdowczyk" sheetId="9" r:id="rId9"/>
+    <sheet name="A. Jędrzejak" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -49,12 +58,886 @@
   <si>
     <t>9.08.2026r.</t>
   </si>
+  <si>
+    <t>22.07.2026r.</t>
+  </si>
+  <si>
+    <t>28.07.2026r.</t>
+  </si>
+  <si>
+    <t>29.07.2026r.</t>
+  </si>
+  <si>
+    <t>26.07.2026r.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie pracuje zarejestrowana w UP w Kaliszu
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>brak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> emeryt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Alkohol - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">nie nadużywa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>brak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bez zmian
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 8.07.2026r. Wizyta u kuratora</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dzioałalność wspólnie z bratem
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> telefon do matki z pytaniem o obecność dozorowanego w domu
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa, 10.07.2026r. Spotkanie AA w Sokołówce
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "Kurier Smaku" jako główny manager , w zastępstwie prowadzeniedokumentacji księgowej firmy, pomoc w kuchni w miarę potrzeby, rozwożenie posiłków
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 15.07.2026r. Wizyta w NZOZ Poradnia Terapii Uzależnień i Współuzależnienia ul. Lipowa 5 Kalisz
+Kolejna wizyta wyznaczona na 5.08.2026r.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>przekazał zaświadczenie lekarskie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>brak
+Ostatni zasiłek z MOPS-u w lipcu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> urlop
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa, 30.07.206r. Aplikacja wszywki przeciwalkoholowej
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>brak
+kontakt z dziećmi telefon czasami</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie pracuje
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa, 30.07.206r. Aplikacja wszywki przeciwalkoholowej
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Anulowano przez S.O. w Kaliszu obowiązkowych wizyt na policji</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> od 13.07. nie pracuje, 28.07. rozmowa kwalifikacyjna w sprawie rozpoczęcia nowej pracy w firmie "Viking" (katering)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Praca -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bez zmian
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Policja -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak jakichkolwiek interwencji
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkohol -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nie nadużywa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Postanowienia -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> brak</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,6 +952,31 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -92,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -103,11 +1011,266 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="40">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -150,10 +1313,100 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C8DA29B3-048F-4122-8306-90FC1373BFBE}" name="Tabela158111317192123" displayName="Tabela158111317192123" ref="B3:C27" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{F6622F0D-A40C-444D-9E56-2E18F96A1A39}" name="dzień wizyty" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{F8DECA46-3CA2-4E04-94C4-70ECC274A4CC}" name="opis zdarzenia" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{50363C8B-1AFA-418F-B4D4-04108227A98D}" name="Tabela15" displayName="Tabela15" ref="C3:D27" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{069E5789-2483-443D-92B8-E5B45070B405}" name="dzień wizyty" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{5543BE6C-BF66-45E7-BDFA-E450BD19ED77}" name="opis zdarzenia" dataDxfId="32"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3E4E74E6-800D-4956-9020-BB6060103117}" name="Tabela158" displayName="Tabela158" ref="C4:D28" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{E631EEBE-9DE6-44FD-8F72-11A089488661}" name="dzień wizyty" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{FB6F5C57-AAD1-41DB-B2F7-2E98B999EF2F}" name="opis zdarzenia" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CD3E6A4B-8942-42DA-89B7-B7F8810A8624}" name="Tabela15811" displayName="Tabela15811" ref="C3:D27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{F74D727D-E19A-48E1-ADE7-91CE167E8353}" name="dzień wizyty" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{17FB8743-6649-43D1-BF44-DF126B67AE24}" name="opis zdarzenia" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{361FEC47-D53F-475C-9056-0B846614B309}" name="Tabela1581113" displayName="Tabela1581113" ref="C3:D27" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{25FE541F-7256-4189-8BC7-B2EA02AA38A1}" name="dzień wizyty" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{281ED8B3-E30B-43DB-9A97-7DC8A5A24329}" name="opis zdarzenia" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{58FD7E7A-C3C6-44F9-A519-D3A48C6E4585}" name="Tabela158111315" displayName="Tabela158111315" ref="C3:D27" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1E953FF1-DFDB-4282-A2D0-4B0B76E147FD}" name="dzień wizyty" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{64DA3924-9B1E-46A3-92EF-407EDB5289DA}" name="opis zdarzenia" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99170262-91FE-442E-A050-FBB00F54B3A0}" name="Tabela158111317" displayName="Tabela158111317" ref="C4:D28" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{EC046F65-0C83-4103-8D54-C4D512932518}" name="dzień wizyty" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{84C45AB6-41A4-45B4-A988-BF1E4D903F5F}" name="opis zdarzenia" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{960F1134-2E84-4E4E-82D2-C8D0A42C7767}" name="Tabela15811131719" displayName="Tabela15811131719" ref="B3:C27" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{F831EBB1-7764-49FA-AA86-967D0273AF56}" name="dzień wizyty" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D32D7367-BC15-4C0B-824F-E89CADB59358}" name="opis zdarzenia" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C06E024D-E730-4A26-9827-27F8102A982D}" name="Tabela1581113171921" displayName="Tabela1581113171921" ref="B3:C27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{2F0BBF5F-BD4F-4C0A-8E25-C7549F437A57}" name="dzień wizyty" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{2F0ECDE7-19FF-4801-924F-A8BC0F57286A}" name="opis zdarzenia" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -598,4 +1851,1253 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F602B2F-9ED5-42E2-895E-7C3B4BBA2FFC}">
+  <dimension ref="B3:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="52.140625" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24DEB22-9C2C-43CC-B239-A1AE18D6A386}">
+  <dimension ref="C3:E28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C69F50-E5F5-4CC4-AAC3-098FBCD3F19A}">
+  <dimension ref="C4:E28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70EABD00-BADE-4810-9B2C-A97AF57FA29F}">
+  <dimension ref="C3:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF2749C-37C6-44B0-A734-8C680DA6F9B5}">
+  <dimension ref="C3:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BCFBAF-3BE6-4DA0-A536-6387BAE58540}">
+  <dimension ref="C3:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="187.5" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="3:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A47AE4-2276-4712-905D-C19F04E8CF29}">
+  <dimension ref="C4:D28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{053DC79D-EB56-4F1F-85CE-F30556EDD1E0}">
+  <dimension ref="B3:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="52.140625" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9982211-1996-4074-9955-DE1BE32953AD}">
+  <dimension ref="B3:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="52.140625" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB37FC5-8EC5-4813-835E-E90721C7D3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149AD205-4421-4E63-B47C-B8C8EED0209C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="435" windowWidth="33810" windowHeight="15345" tabRatio="653" activeTab="9" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="653" activeTab="9" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -931,6 +931,9 @@
       </rPr>
       <t xml:space="preserve"> brak</t>
     </r>
+  </si>
+  <si>
+    <t>piłka</t>
   </si>
 </sst>
 </file>
@@ -1313,100 +1316,100 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{857DDC40-40FC-4A22-99AF-F7A81BB5DBE1}" name="Tabela1" displayName="Tabela1" ref="D6:E30" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{F3DF247F-755A-47F2-86B3-BD1B61626E89}" name="dzień wizyty" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D6AD5300-A470-4D91-82E8-74158275FAE2}" name="opis zdarzenia" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C8DA29B3-048F-4122-8306-90FC1373BFBE}" name="Tabela158111317192123" displayName="Tabela158111317192123" ref="B3:C27" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C8DA29B3-048F-4122-8306-90FC1373BFBE}" name="Tabela158111317192123" displayName="Tabela158111317192123" ref="B3:C27" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F6622F0D-A40C-444D-9E56-2E18F96A1A39}" name="dzień wizyty" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{F8DECA46-3CA2-4E04-94C4-70ECC274A4CC}" name="opis zdarzenia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F6622F0D-A40C-444D-9E56-2E18F96A1A39}" name="dzień wizyty" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{F8DECA46-3CA2-4E04-94C4-70ECC274A4CC}" name="opis zdarzenia" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{50363C8B-1AFA-418F-B4D4-04108227A98D}" name="Tabela15" displayName="Tabela15" ref="C3:D27" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{50363C8B-1AFA-418F-B4D4-04108227A98D}" name="Tabela15" displayName="Tabela15" ref="C3:D27" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{069E5789-2483-443D-92B8-E5B45070B405}" name="dzień wizyty" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{5543BE6C-BF66-45E7-BDFA-E450BD19ED77}" name="opis zdarzenia" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{069E5789-2483-443D-92B8-E5B45070B405}" name="dzień wizyty" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{5543BE6C-BF66-45E7-BDFA-E450BD19ED77}" name="opis zdarzenia" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3E4E74E6-800D-4956-9020-BB6060103117}" name="Tabela158" displayName="Tabela158" ref="C4:D28" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3E4E74E6-800D-4956-9020-BB6060103117}" name="Tabela158" displayName="Tabela158" ref="C4:D28" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E631EEBE-9DE6-44FD-8F72-11A089488661}" name="dzień wizyty" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{FB6F5C57-AAD1-41DB-B2F7-2E98B999EF2F}" name="opis zdarzenia" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{E631EEBE-9DE6-44FD-8F72-11A089488661}" name="dzień wizyty" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{FB6F5C57-AAD1-41DB-B2F7-2E98B999EF2F}" name="opis zdarzenia" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CD3E6A4B-8942-42DA-89B7-B7F8810A8624}" name="Tabela15811" displayName="Tabela15811" ref="C3:D27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{CD3E6A4B-8942-42DA-89B7-B7F8810A8624}" name="Tabela15811" displayName="Tabela15811" ref="C3:D27" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F74D727D-E19A-48E1-ADE7-91CE167E8353}" name="dzień wizyty" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{17FB8743-6649-43D1-BF44-DF126B67AE24}" name="opis zdarzenia" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{F74D727D-E19A-48E1-ADE7-91CE167E8353}" name="dzień wizyty" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{17FB8743-6649-43D1-BF44-DF126B67AE24}" name="opis zdarzenia" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{361FEC47-D53F-475C-9056-0B846614B309}" name="Tabela1581113" displayName="Tabela1581113" ref="C3:D27" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{361FEC47-D53F-475C-9056-0B846614B309}" name="Tabela1581113" displayName="Tabela1581113" ref="C3:D27" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{25FE541F-7256-4189-8BC7-B2EA02AA38A1}" name="dzień wizyty" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{281ED8B3-E30B-43DB-9A97-7DC8A5A24329}" name="opis zdarzenia" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{25FE541F-7256-4189-8BC7-B2EA02AA38A1}" name="dzień wizyty" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{281ED8B3-E30B-43DB-9A97-7DC8A5A24329}" name="opis zdarzenia" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{58FD7E7A-C3C6-44F9-A519-D3A48C6E4585}" name="Tabela158111315" displayName="Tabela158111315" ref="C3:D27" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{58FD7E7A-C3C6-44F9-A519-D3A48C6E4585}" name="Tabela158111315" displayName="Tabela158111315" ref="C3:D27" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1E953FF1-DFDB-4282-A2D0-4B0B76E147FD}" name="dzień wizyty" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{64DA3924-9B1E-46A3-92EF-407EDB5289DA}" name="opis zdarzenia" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{1E953FF1-DFDB-4282-A2D0-4B0B76E147FD}" name="dzień wizyty" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{64DA3924-9B1E-46A3-92EF-407EDB5289DA}" name="opis zdarzenia" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99170262-91FE-442E-A050-FBB00F54B3A0}" name="Tabela158111317" displayName="Tabela158111317" ref="C4:D28" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{99170262-91FE-442E-A050-FBB00F54B3A0}" name="Tabela158111317" displayName="Tabela158111317" ref="C4:D28" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{EC046F65-0C83-4103-8D54-C4D512932518}" name="dzień wizyty" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{84C45AB6-41A4-45B4-A988-BF1E4D903F5F}" name="opis zdarzenia" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{EC046F65-0C83-4103-8D54-C4D512932518}" name="dzień wizyty" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{84C45AB6-41A4-45B4-A988-BF1E4D903F5F}" name="opis zdarzenia" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{960F1134-2E84-4E4E-82D2-C8D0A42C7767}" name="Tabela15811131719" displayName="Tabela15811131719" ref="B3:C27" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{960F1134-2E84-4E4E-82D2-C8D0A42C7767}" name="Tabela15811131719" displayName="Tabela15811131719" ref="B3:C27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F831EBB1-7764-49FA-AA86-967D0273AF56}" name="dzień wizyty" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D32D7367-BC15-4C0B-824F-E89CADB59358}" name="opis zdarzenia" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{F831EBB1-7764-49FA-AA86-967D0273AF56}" name="dzień wizyty" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D32D7367-BC15-4C0B-824F-E89CADB59358}" name="opis zdarzenia" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C06E024D-E730-4A26-9827-27F8102A982D}" name="Tabela1581113171921" displayName="Tabela1581113171921" ref="B3:C27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{C06E024D-E730-4A26-9827-27F8102A982D}" name="Tabela1581113171921" displayName="Tabela1581113171921" ref="B3:C27" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2F0BBF5F-BD4F-4C0A-8E25-C7549F437A57}" name="dzień wizyty" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{2F0ECDE7-19FF-4801-924F-A8BC0F57286A}" name="opis zdarzenia" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{2F0BBF5F-BD4F-4C0A-8E25-C7549F437A57}" name="dzień wizyty" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{2F0ECDE7-19FF-4801-924F-A8BC0F57286A}" name="opis zdarzenia" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1968,7 +1971,9 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149AD205-4421-4E63-B47C-B8C8EED0209C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A14508-CB8A-44AE-BB62-C94A8A2504D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="653" activeTab="9" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -931,9 +931,6 @@
       </rPr>
       <t xml:space="preserve"> brak</t>
     </r>
-  </si>
-  <si>
-    <t>piłka</t>
   </si>
 </sst>
 </file>
@@ -1971,9 +1968,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="C27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dozorowani.xlsx
+++ b/dozorowani.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grzegorz\Desktop\dozorowani\dozorowani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A14508-CB8A-44AE-BB62-C94A8A2504D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F631A0-602C-46BA-85E1-05181B81E2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="653" activeTab="9" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="653" activeTab="7" xr2:uid="{059A9DF4-84C4-4EA8-B85B-126989365D06}"/>
   </bookViews>
   <sheets>
     <sheet name="S. Gieszczyński" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>opis zdarzenia</t>
   </si>
@@ -931,6 +931,9 @@
       </rPr>
       <t xml:space="preserve"> brak</t>
     </r>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -2967,7 +2970,9 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
